--- a/artfynd/A 8227-2026 artfynd.xlsx
+++ b/artfynd/A 8227-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133646052</v>
       </c>
       <c r="B2" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133646478</v>
       </c>
       <c r="B3" t="n">
-        <v>93206</v>
+        <v>93208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8227-2026 artfynd.xlsx
+++ b/artfynd/A 8227-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133646052</v>
       </c>
       <c r="B2" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133646478</v>
       </c>
       <c r="B3" t="n">
-        <v>93208</v>
+        <v>93216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8227-2026 artfynd.xlsx
+++ b/artfynd/A 8227-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133646052</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133646478</v>
       </c>
       <c r="B3" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8227-2026 artfynd.xlsx
+++ b/artfynd/A 8227-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133646052</v>
+        <v>133646478</v>
       </c>
       <c r="B2" t="n">
-        <v>98053</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>787946</v>
+        <v>787818</v>
       </c>
       <c r="R2" t="n">
-        <v>7248763</v>
+        <v>7248995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gamla</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133646478</v>
+        <v>133646052</v>
       </c>
       <c r="B3" t="n">
-        <v>93264</v>
+        <v>98060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787818</v>
+        <v>787946</v>
       </c>
       <c r="R3" t="n">
-        <v>7248995</v>
+        <v>7248763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,17 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gamla</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 8227-2026 artfynd.xlsx
+++ b/artfynd/A 8227-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646478</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,8 +881,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646052</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>